--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484076_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484076_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. COFFIE</t>
+          <t>J. MARTIN MONZON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0695</v>
+        <v>3.7845</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4941</v>
+        <v>6.047</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4247</v>
+        <v>-2.2625</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6312</v>
+        <v>4.8477</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0284</v>
+        <v>2.666</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6028</v>
+        <v>2.1817</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8463</v>
+        <v>7.4482</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7579</v>
+        <v>4.3857</v>
       </c>
       <c r="L2" t="n">
-        <v>2.0884</v>
+        <v>3.0625</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2151</v>
+        <v>-2.6004</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7294</v>
+        <v>-1.7197</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4856</v>
+        <v>-0.8808</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0452</v>
+        <v>-1.2697</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9807</v>
+        <v>-0.6914</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0644</v>
+        <v>-0.5783</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1947</v>
+        <v>0.6032</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1425</v>
+        <v>1.4724</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3373</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTIN MONZON</t>
+          <t>D. COFFIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0588</v>
+        <v>2.6105</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9846</v>
+        <v>3.3718</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9259</v>
+        <v>-0.7614</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8477</v>
+        <v>2.6312</v>
       </c>
       <c r="H3" t="n">
-        <v>2.666</v>
+        <v>1.0284</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1817</v>
+        <v>1.6028</v>
       </c>
       <c r="J3" t="n">
-        <v>7.4482</v>
+        <v>4.8463</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3857</v>
+        <v>2.7579</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0625</v>
+        <v>2.0884</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6004</v>
+        <v>-2.2151</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7197</v>
+        <v>-1.7294</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8808</v>
+        <v>-0.4856</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9954</v>
+        <v>-0.4138</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7537</v>
+        <v>-0.1416</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2417</v>
+        <v>-0.2722</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6032</v>
+        <v>0.1947</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4724</v>
+        <v>-0.1425</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8692</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3601</v>
+        <v>0.6188</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6106</v>
+        <v>-0.5483</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9707</v>
+        <v>1.1671</v>
       </c>
       <c r="G4" t="n">
         <v>4.2309</v>
@@ -766,13 +766,13 @@
         <v>1.1903</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0934</v>
+        <v>-0.8347</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4988</v>
+        <v>-0.4364</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5947</v>
+        <v>-0.3983</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0362</v>
+        <v>0.3806</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7278</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.764</v>
+        <v>0.9043</v>
       </c>
       <c r="G5" t="n">
         <v>0.1358</v>
@@ -844,13 +844,13 @@
         <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9607</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3741</v>
+        <v>-0.17</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5867</v>
+        <v>-0.4464</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0213</v>
+        <v>-0.1904</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1206</v>
+        <v>-1.5287</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1419</v>
+        <v>1.3383</v>
       </c>
       <c r="G6" t="n">
         <v>0.7912</v>
@@ -922,13 +922,13 @@
         <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3055</v>
+        <v>-0.5172</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2438</v>
+        <v>-0.1643</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5493</v>
+        <v>-0.3529</v>
       </c>
       <c r="V6" t="n">
         <v>-0.266</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2496</v>
+        <v>-0.7409</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8469</v>
+        <v>-1.4785</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.7376</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4678</v>
@@ -1000,13 +1000,13 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3689</v>
+        <v>-0.8602</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7481</v>
+        <v>-0.3797</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6207</v>
+        <v>-0.4804</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8924</v>
+        <v>-1.4703</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5673</v>
+        <v>1.2418</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4596</v>
+        <v>-2.7121</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9644</v>
@@ -1078,13 +1078,13 @@
         <v>2.1822</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9199</v>
+        <v>-1.4979</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5586</v>
+        <v>-0.8841</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3613</v>
+        <v>-0.6138</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.0864</v>
+        <v>-4.8441</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6926</v>
+        <v>-3.5906</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3938</v>
+        <v>-1.2535</v>
       </c>
       <c r="G9" t="n">
         <v>-2.599</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0231</v>
+        <v>-0.7808</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5611</v>
+        <v>-0.4591</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.462</v>
+        <v>-0.3217</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8692</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.0992</v>
+        <v>-6.0088</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9068</v>
+        <v>-2.8444</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1924</v>
+        <v>-3.1644</v>
       </c>
       <c r="G10" t="n">
         <v>0.2069</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.132</v>
+        <v>-1.0416</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.442</v>
+        <v>-0.3797</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6899</v>
+        <v>-0.6619</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.5041</v>
+        <v>-10.1138</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.6591</v>
+        <v>-7.353</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.845</v>
+        <v>-2.7608</v>
       </c>
       <c r="G11" t="n">
         <v>-5.986</v>
@@ -1312,13 +1312,13 @@
         <v>0.7935</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1455</v>
+        <v>-0.7553</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.3174</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5221</v>
+        <v>-0.4379</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.2858</v>
+        <v>-15.9739</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.5184</v>
+        <v>-7.206600000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.7675</v>
+        <v>-8.7674</v>
       </c>
       <c r="G12" t="n">
         <v>1.826499999999999</v>
@@ -1390,13 +1390,13 @@
         <v>12.895</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.8992</v>
+        <v>-8.5876</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.3354</v>
+        <v>-4.0237</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.564</v>
+        <v>-4.5638</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2778</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1352</v>
+        <v>4.14</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7044</v>
+        <v>1.834</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4308</v>
+        <v>2.306</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5124</v>
+        <v>-1.568</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2649</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2476</v>
+        <v>-0.7721</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8832</v>
+        <v>-0.058</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3158</v>
+        <v>0.3385</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5674</v>
+        <v>-0.3965</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6293</v>
+        <v>-1.51</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0509</v>
+        <v>-1.1343</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6802</v>
+        <v>-0.3756</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1984</v>
+        <v>2.7774</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>2.7774</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0871</v>
+        <v>0.7836</v>
       </c>
       <c r="T13" t="n">
-        <v>1.797</v>
+        <v>0.4195</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2901</v>
+        <v>0.3641</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.266</v>
+        <v>2.1469</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8364</v>
+        <v>3.2271</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2218</v>
+        <v>-0.3159</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6146</v>
+        <v>3.543</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.568</v>
+        <v>2.5124</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7959000000000001</v>
+        <v>1.2649</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7721</v>
+        <v>1.2476</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.058</v>
+        <v>1.8832</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3385</v>
+        <v>1.3158</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3965</v>
+        <v>0.5674</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.51</v>
+        <v>0.6293</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1343</v>
+        <v>-0.0509</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3756</v>
+        <v>0.6802</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7774</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R14" t="n">
         <v>2.7774</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4801</v>
+        <v>1.179</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1926</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6727</v>
+        <v>0.4024</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1469</v>
+        <v>-0.266</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9786</v>
+        <v>2.7109</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4199</v>
+        <v>3.4035</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5587</v>
+        <v>-0.6926</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0005</v>
+        <v>-0.0264</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5783</v>
+        <v>-0.7154</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5778</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1.44</v>
+        <v>2.4998</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0374</v>
+        <v>0.3533</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5973000000000001</v>
+        <v>2.1464</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4395</v>
+        <v>-2.5262</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.459</v>
+        <v>-1.0688</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0195</v>
+        <v>-1.4574</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.579</v>
+        <v>1.3887</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6688</v>
+        <v>0.7454</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0431</v>
+        <v>0.3005</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6257</v>
+        <v>0.4449</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2777</v>
+        <v>0.6032</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0713</v>
+        <v>0.6032</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8795</v>
+        <v>2.2489</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9807</v>
+        <v>-1.0473</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1012</v>
+        <v>3.2962</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7164</v>
+        <v>-0.8619</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0051</v>
+        <v>-0.1662</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7215</v>
+        <v>-0.6957</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>-1.5519</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6787</v>
+        <v>-0.312</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3213</v>
+        <v>-1.2399</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7164</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6736</v>
+        <v>0.1458</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0428</v>
+        <v>0.5442</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3968</v>
+        <v>2.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3887</v>
+        <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5246</v>
+        <v>0.7978</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9726</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.552</v>
+        <v>0.2933</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6953</v>
+        <v>2.2083</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7413</v>
+        <v>0.7057</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4365</v>
+        <v>1.5026</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8619</v>
+        <v>1.0005</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1662</v>
+        <v>1.5783</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6957</v>
+        <v>-0.5778</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5519</v>
+        <v>1.44</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.312</v>
+        <v>2.0374</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2399</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.4395</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1458</v>
+        <v>-0.459</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5442</v>
+        <v>0.0195</v>
       </c>
       <c r="P17" t="n">
-        <v>2.579</v>
+        <v>1.5871</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
         <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2442</v>
+        <v>0.8984</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8106</v>
+        <v>0.3289</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4335</v>
+        <v>0.5696</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.266</v>
+        <v>-1.2777</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5731</v>
+        <v>1.599</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0974</v>
+        <v>1.7564</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5243</v>
+        <v>-0.1573</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0264</v>
+        <v>-0.7164</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7154</v>
+        <v>0.0051</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6889999999999999</v>
+        <v>-0.7215</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4998</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3533</v>
+        <v>1.6787</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1464</v>
+        <v>0.3213</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5262</v>
+        <v>-2.7164</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0688</v>
+        <v>-1.6736</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4574</v>
+        <v>-1.0428</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
         <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6076</v>
+        <v>1.2442</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0056</v>
+        <v>0.7483</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6132</v>
+        <v>0.4959</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6032</v>
+        <v>0.6745</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3317</v>
+        <v>1.4463</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1642</v>
+        <v>3.0824</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8325</v>
+        <v>-1.6361</v>
       </c>
       <c r="G19" t="n">
         <v>-1.009</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6513</v>
+        <v>0.4634</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7481</v>
+        <v>0.1701</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0969</v>
+        <v>0.2933</v>
       </c>
       <c r="V19" t="n">
         <v>0.6032</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1071</v>
+        <v>1.1196</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2026</v>
+        <v>0.8853</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0955</v>
+        <v>0.2343</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0562</v>
+        <v>-0.9933</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7258</v>
+        <v>-0.4438</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3303</v>
+        <v>-0.5495</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9515</v>
+        <v>0.8002</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3816</v>
+        <v>0.4234</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5699</v>
+        <v>0.3768</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8953</v>
+        <v>-1.7934</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6558</v>
+        <v>-0.8672</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2396</v>
+        <v>-0.9263</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0509</v>
+        <v>0.129</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6236</v>
+        <v>0.0851</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4273</v>
+        <v>0.0439</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0151</v>
+        <v>0.2295</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.135</v>
+        <v>0.1005</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1501</v>
+        <v>0.1289</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9933</v>
+        <v>1.0562</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4438</v>
+        <v>0.7258</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5495</v>
+        <v>0.3303</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8002</v>
+        <v>1.9515</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4234</v>
+        <v>1.3816</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3768</v>
+        <v>0.5699</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7934</v>
+        <v>-0.8953</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8672</v>
+        <v>-0.6558</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9263</v>
+        <v>-0.2396</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9838</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9838</v>
+        <v>2.1822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9755</v>
+        <v>1.1733</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9352</v>
+        <v>0.5216</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0403</v>
+        <v>0.6518</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4847</v>
+        <v>-1.2245</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1007</v>
+        <v>0.1033</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.384</v>
+        <v>-1.3279</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0776</v>
@@ -2170,13 +2170,13 @@
         <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3945</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3175</v>
+        <v>0.5215</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0771</v>
+        <v>0.1332</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7814</v>
+        <v>-1.4192</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0465</v>
+        <v>-1.7404</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2651</v>
+        <v>0.3212</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1431</v>
@@ -2248,13 +2248,13 @@
         <v>1.3887</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4682</v>
+        <v>0.8304</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1189</v>
+        <v>0.1871</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.6433</v>
       </c>
       <c r="V23" t="n">
         <v>1.4724</v>
@@ -2287,7 +2287,7 @@
         <v>8.767500000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>7.518300000000002</v>
+        <v>7.518300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8266</v>
@@ -2311,7 +2311,7 @@
         <v>-13.4436</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.614600000000001</v>
+        <v>-7.6146</v>
       </c>
       <c r="O24" t="n">
         <v>-5.8291</v>
@@ -2329,10 +2329,10 @@
         <v>8.8992</v>
       </c>
       <c r="T24" t="n">
-        <v>4.564</v>
+        <v>4.5638</v>
       </c>
       <c r="U24" t="n">
-        <v>4.3354</v>
+        <v>4.3357</v>
       </c>
       <c r="V24" t="n">
         <v>1.2775</v>
